--- a/OCT_2026/10-15-26/Furqan.xlsx
+++ b/OCT_2026/10-15-26/Furqan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE01419C-A5F4-465D-9BE8-9FCD48BDD353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD431811-8483-47F6-BE64-019BDFE3E777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8528,7 +8528,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -9954,7 +9954,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -11376,7 +11376,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -12798,7 +12798,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -47892,7 +47892,7 @@
       <c r="L4" s="395"/>
       <c r="M4" s="398">
         <f ca="1">TODAY()+1</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="N4" s="398"/>
       <c r="O4" s="398"/>
@@ -47920,7 +47920,7 @@
       <c r="L5" s="395"/>
       <c r="M5" s="398">
         <f ca="1">M4-1</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="N5" s="394"/>
       <c r="O5" s="394"/>
@@ -56956,7 +56956,7 @@
     <mergeCell ref="N8:P8"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>$XFC$3:$XFC$4</formula1>
     </dataValidation>
@@ -58378,7 +58378,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -59804,7 +59804,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -61226,7 +61226,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -62652,7 +62652,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
